--- a/notes/tiempos_medidos_ModuloC_v3.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v3.xlsx
@@ -21,13 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +70,12 @@
       <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -100,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,6 +140,9 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1059,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1080,10 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1082,7 +1096,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Medido sobre la placa el 2026-10-09, con el planificador por tiempo ya funcionando. Es el tiempo del sensor en sí: no incluye la pausa obligatoria que viene después ni el arranque de la placa.</t>
+          <t>MEDICION LIMPIA: 75 minutos seguidos sobre el firmware definitivo, sin reflashear ni tocar la placa durante la captura. Los valores del libro anterior venian de logs recogidos entre versiones distintas del firmware; estos no.</t>
         </is>
       </c>
     </row>
@@ -1130,6 +1144,28 @@
           <t>Nota</t>
         </is>
       </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>LIMPIA
+(s)</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Rango limpio
+(s)</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Dispersión</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1165,6 +1201,20 @@
           <t>Lectura rápida, con el calefactor APAGADO. Idéntica en 44 medidas: no varía nada.</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>0,039 – 0,039</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="39" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -1198,6 +1248,20 @@
           <t>Lectura completa, calefactor a 320 °C. En el libro anterior no existía por separado: era parte del "burst". La hoja original decía 10,8 s; son 0,188.</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>0,188 – 0,188</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="39" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -1233,6 +1297,20 @@
           <t>Sin cambio, y clavado. Incluye el ciclo de alimentación y el calentamiento: es un sensor de disparo único que mide al arrancar.</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>3,513 – 3,513</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -1268,6 +1346,20 @@
           <t>El láser. Su arranque de 5 s ya NO se paga en cada despertar: solo cuando le toca medir.</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n">
+        <v>2.114</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>2,114 – 2,133</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="n">
+        <v>0.009000000000000001</v>
+      </c>
     </row>
     <row r="9" ht="39" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1303,8 +1395,22 @@
           <t>Va cableado directo a corriente, siempre caliente. Sus 210 s de estabilización se pagan una vez al energizar la placa, no por lectura.</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="39" customHeight="1">
+      <c r="I9" s="12" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>0,024 – 0,024</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Calypso</t>
@@ -1335,8 +1441,22 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>EL MÁS VARIABLE de los seis, por un factor de 25. Escucha hasta 1,5 s esperando una trama NMEA válida; si llega pronto termina antes.</t>
-        </is>
+          <t>ATENCIÓN: ese 1,501 s NO es lo que tarda en leer, es lo que tarda en RENDIRSE. Cinco de siete veces agotó la ventana de 1,5 s sin recibir una trama NMEA válida; las otras dos llegaron en 101 y 219 ms. Cuando sí responde da 0,0 m/s con validez 1, que en interior es correcto. El sensor está marginal, no muerto.</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>0,101 – 1,502</t>
+        </is>
+      </c>
+      <c r="L10" s="25" t="n">
+        <v>0.9329999999999999</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -1353,6 +1473,83 @@
         <is>
           <t>Solo los sensores. Un barrido completo medido dura 19,554 s, así que casi dos tercios del tiempo son las pausas obligatorias entre sensor y sensor.</t>
         </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>CADENCIA MEDIDA EN LA CAPTURA LIMPIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Despertares capturados</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>En 75 minutos.</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" ht="39" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo mediano (s)</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Entre despertares separados más de 60 s. Configurado: 300 s -&gt; 1,1% de desviación. Con el planificador por ticks era del 88%.</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>296.7</v>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo mínimo (s)</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>No todos los huecos son el periodo de 5 min: el envío va desplazado +1 minuto y genera despertares propios.</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>238.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Intervalo máximo (s)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Envíos por radio</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Lotes de 1 a 8 lecturas. Los de 8 llenan el almacén justo, que es para lo que se dimensionó.</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/notes/tiempos_medidos_ModuloC_v3.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v3.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,6 +143,10 @@
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1566,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1579,6 +1583,9 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="54" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1653,6 +1660,22 @@
           <t>Nota</t>
         </is>
       </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>MEDIDO
+prealarma (s)</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1695,6 +1718,16 @@
           <t>La señal que más rápido se mueve en un incendio, y la más barata de leer: 40 ms.</t>
         </is>
       </c>
+      <c r="K5" s="21" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="M5" s="27">
+        <f>K5/(D5*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -1737,6 +1770,16 @@
           <t>El mismo chip, otra operación: enciende el calefactor a 320 °C.</t>
         </is>
       </c>
+      <c r="K6" s="21" t="n">
+        <v>600</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" s="27">
+        <f>K6/(D6*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -1779,6 +1822,14 @@
           <t>EL ÚNICO QUE NO SE ACELERA, a propósito. Es el sensor menos fiable de la caja.</t>
         </is>
       </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>n insuficiente</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -1821,6 +1872,16 @@
           <t>Confirma un incendio más que detectarlo: está siempre alimentado y caliente.</t>
         </is>
       </c>
+      <c r="K8" s="21" t="n">
+        <v>599.5</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="27">
+        <f>K8/(D8*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1863,6 +1924,16 @@
           <t>El humo es la firma más específica, pero el láser consume 68 mA.</t>
         </is>
       </c>
+      <c r="K9" s="21" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" s="27">
+        <f>K9/(D9*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -1905,6 +1976,16 @@
           <t>Constante en los tres estados. Importa para saber hacia dónde se propagaría.</t>
         </is>
       </c>
+      <c r="K10" s="21" t="n">
+        <v>300.1</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" s="27">
+        <f>K10/(D10*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
@@ -1947,6 +2028,16 @@
           <t>En NORMAL va desplazado +1 minuto: en el minuto 30 vencen cinco lecturas a la vez y el barrido tarda 19,6 s, así que transmitir en el minuto exacto mandaría las partículas a medias. NO es un periodo de 31 min, que derivaría.</t>
         </is>
       </c>
+      <c r="K12" s="21" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="27">
+        <f>K12/(D12*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1974,10 +2065,10 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Lecturas acumuladas</t>
+          <t>Lecturas acumuladas (estimado)</t>
         </is>
       </c>
       <c r="C16" s="20">
@@ -1992,6 +2083,11 @@
         <f>E12/E15</f>
         <v/>
       </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>ESTA CUENTA SE QUEDA CORTA. Divide el envío entre el periodo más corto, pero los sensores no comparten rejilla: con T/H/P cada 3 min y viento cada 5, los barridos caen en la UNIÓN de las dos series, no en la más rápida. En prealarma la estimación da 5 y lo medido son 8.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2031,6 +2127,21 @@
       <c r="E18">
         <f>IF(E16&lt;=E17,"sí","NO - se pierden")</f>
         <v/>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Lecturas por envío, MEDIDAS</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>Tres envíos en 55 min, los tres con 8 lecturas en 3 paquetes de radio. OCHO ES EXACTAMENTE LA CAPACIDAD DEL ALMACÉN: en prealarma no sobra ni una. Si se acelerase cualquier periodo, o si un envío fallara, se empezarían a perder lecturas.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/notes/tiempos_medidos_ModuloC_v3.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v3.xlsx
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="78" customHeight="1">
+    <row r="10" ht="92" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Calypso</t>
@@ -1443,20 +1443,22 @@
         <f>IF(C10=0,"",D10/C10)</f>
         <v/>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>ATENCIÓN: ese 1,501 s NO es lo que tarda en leer, es lo que tarda en RENDIRSE. Cinco de siete veces agotó la ventana de 1,5 s sin recibir una trama NMEA válida; las otras dos llegaron en 101 y 219 ms. Cuando sí responde da 0,0 m/s con validez 1, que en interior es correcto. El sensor está marginal, no muerto.</t>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>CIFRA CORREGIDA el 2026-10-11, y hay que leerla con cuidado. El 1,501 s anterior era lo que tardaba en RENDIRSE sin recibir trama, no en leer: se le preguntaba 1,5 s después de encenderlo y el sensor necesita ~20 s de arranque. Dándoselos, contesta en 40-521 ms. PERO en estado normal el nodo pierde la alimentación en cada sueño, así que el slot incluye además la espera de arranque y mide ~16 s. Para el presupuesto energético cuenta ese 16, no el 0,5.</t>
         </is>
       </c>
       <c r="I10" s="12" t="n">
-        <v>1.501</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>7</v>
+        <v>0.52</v>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>ver nota</t>
+        </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>0,101 – 1,502</t>
+          <t>0,040 – 0,521</t>
         </is>
       </c>
       <c r="L10" s="25" t="n">
@@ -1570,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1586,6 +1588,9 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1676,6 +1681,22 @@
           <t>Error</t>
         </is>
       </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>MEDIDO
+alarma (s)</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1728,6 +1749,16 @@
         <f>K5/(D5*60)-1</f>
         <v/>
       </c>
+      <c r="N5" s="21" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" s="27">
+        <f>N5/(E5*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -1780,6 +1811,16 @@
         <f>K6/(D6*60)-1</f>
         <v/>
       </c>
+      <c r="N6" s="21" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="27">
+        <f>N6/(E6*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -1830,6 +1871,11 @@
       <c r="L7" s="13" t="n">
         <v>1</v>
       </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>n insuficiente</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -1882,6 +1928,16 @@
         <f>K8/(D8*60)-1</f>
         <v/>
       </c>
+      <c r="N8" s="21" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="27">
+        <f>N8/(E8*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1934,6 +1990,16 @@
         <f>K9/(D9*60)-1</f>
         <v/>
       </c>
+      <c r="N9" s="21" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="27">
+        <f>N9/(E9*60)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -1984,6 +2050,16 @@
       </c>
       <c r="M10" s="27">
         <f>K10/(D10*60)-1</f>
+        <v/>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>300.3</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="27">
+        <f>N10/(E10*60)-1</f>
         <v/>
       </c>
     </row>
@@ -2450,7 +2526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2572,6 +2648,30 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="92" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>HAY UN TRANSITORIO DE ~7 MINUTOS</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Tras grabar el firmware, los intervalos no significan nada durante unos 7 minutos, y medir sin descartarlos lleva a conclusiones falsas: en alarma los trabajos de 300 s parecían ir un 20-27% adelantados, y con el transitorio fuera salen a 300,2 s. Dos cosas lo causan, encadenadas: el arranque en frío fuerza a TODOS los trabajos a vencer a la vez, así que la primera ronda cae fuera de la rejilla del reloj; y la primera sincronización con Módulo B llega ~35 s después y RE-FASEA el calendario entero, porque la base de tiempo salta del tiempo propio del nodo a la época real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>EL LOG PIERDE LÍNEAS EN NORMAL</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>En estado normal el nodo se duerme milisegundos después de imprimir, y el puerto USB se cae con él: parte de las líneas no llegan al PC. Por eso los intervalos contados sobre el log salen largos. El dato fiable de cuántas lecturas hizo de verdad es CUÁNTAS LLEVA CADA ENVÍO, porque esa cuenta la lleva el nodo. En prealarma y alarma no pasa, porque ahí no duerme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
